--- a/员工档案导入模板.xlsx
+++ b/员工档案导入模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YuJianHui\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2E9159-8ACE-4855-89E9-78E5677A39D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B111273-AE52-4D24-8E12-85C00C4721F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="员工主表" sheetId="1" r:id="rId1"/>
@@ -24,13 +24,14 @@
     <sheet name="奖惩记录" sheetId="9" r:id="rId9"/>
     <sheet name="入职前工作经历" sheetId="10" r:id="rId10"/>
     <sheet name="薪酬调整记录" sheetId="11" r:id="rId11"/>
+    <sheet name="飞书账号映射" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="319">
   <si>
     <t>员工主表</t>
   </si>
@@ -981,6 +982,22 @@
   </si>
   <si>
     <t>于伟</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名[冗余]_real_name</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞书UserID_feishu_user_id</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞书账号映射</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>【说明】唯一键=身份证号；每个员工一行记录。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1075,7 +1092,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1113,11 +1130,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1134,6 +1160,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2077,6 +2109,64 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F4F926-84E2-4685-8885-92568A769B43}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/员工档案导入模板.xlsx
+++ b/员工档案导入模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YuJianHui\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B111273-AE52-4D24-8E12-85C00C4721F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10495F9-40C2-48A2-A527-1188915E07DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="322">
   <si>
     <t>员工主表</t>
   </si>
@@ -808,9 +808,6 @@
   </si>
   <si>
     <t>奖惩记录</t>
-  </si>
-  <si>
-    <t>【说明】唯一键=身份证号+日期+类型；新增记录直接追加行。</t>
   </si>
   <si>
     <t>类型_record_type</t>
@@ -998,6 +995,22 @@
   </si>
   <si>
     <t>【说明】唯一键=身份证号；每个员工一行记录。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>530102198805151234</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>530102198805151235</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>【说明】唯一键=身份证号+类型+日期；新增记录直接追加行。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2222</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1059,7 +1072,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1091,8 +1104,14 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1139,11 +1158,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1154,18 +1182,34 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1473,7 +1517,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="6" customWidth="1"/>
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
@@ -1500,68 +1544,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
     </row>
     <row r="3" spans="1:25" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1636,10 +1680,10 @@
     </row>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>308</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>318</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>29</v>
@@ -1678,7 +1722,7 @@
         <v>37</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>38</v>
@@ -1713,10 +1757,10 @@
     </row>
     <row r="5" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B5" s="2">
-        <v>5.3010219880515098E+17</v>
+        <v>313</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -1755,7 +1799,7 @@
         <v>37</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>38</v>
@@ -1805,151 +1849,151 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -1959,6 +2003,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1968,7 +2013,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1979,51 +2024,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>59</v>
@@ -2035,14 +2080,14 @@
         <v>61</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2067,14 +2112,14 @@
         <v>99</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2093,13 +2138,13 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -2115,48 +2160,59 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F4F926-84E2-4685-8885-92568A769B43}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>1111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2176,19 +2232,19 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="21.77734375" bestFit="1" customWidth="1"/>
@@ -2200,114 +2256,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
     </row>
     <row r="2" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
     </row>
     <row r="3" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>66</v>
@@ -2336,55 +2392,55 @@
     </row>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="2">
+      <c r="P4" s="2">
         <v>6000</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>85</v>
@@ -2415,53 +2471,53 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="N5" s="2">
+      <c r="P5" s="2">
         <v>15000</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>85</v>
@@ -2492,52 +2548,52 @@
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="N6" s="2">
+      <c r="P6" s="2">
         <v>35000</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q6" s="2"/>
       <c r="R6" s="2" t="s">
         <v>85</v>
       </c>
@@ -2568,6 +2624,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2577,18 +2634,18 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.21875" bestFit="1" customWidth="1"/>
@@ -2596,86 +2653,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>129</v>
@@ -2694,41 +2751,41 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="N4" s="2">
         <v>4</v>
@@ -2747,41 +2804,41 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="N5" s="2">
         <v>3</v>
@@ -2803,6 +2860,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2812,7 +2870,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -2825,43 +2883,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
     </row>
     <row r="3" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2893,7 +2951,7 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2928,7 +2986,7 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2944,7 +3002,7 @@
         <v>174</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>175</v>
@@ -2975,54 +3033,54 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>182</v>
@@ -3032,20 +3090,20 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>183</v>
@@ -3055,20 +3113,20 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>185</v>
@@ -3078,20 +3136,20 @@
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>187</v>
@@ -3104,6 +3162,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3113,7 +3172,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
@@ -3125,44 +3184,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>191</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -3188,7 +3247,7 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3220,7 +3279,7 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3264,66 +3323,66 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>217</v>
@@ -3333,26 +3392,26 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>114</v>
@@ -3362,26 +3421,26 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>114</v>
@@ -3391,26 +3450,26 @@
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>235</v>
@@ -3423,6 +3482,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3432,63 +3492,63 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>243</v>
@@ -3501,23 +3561,23 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>245</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>250</v>
@@ -3530,23 +3590,23 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>252</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>257</v>
@@ -3562,6 +3622,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3571,7 +3632,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.77734375" bestFit="1" customWidth="1"/>
@@ -3579,91 +3640,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>76</v>
